--- a/artifacts/ETH_USDT/metrics/ETH_USDT_metrics.xlsx
+++ b/artifacts/ETH_USDT/metrics/ETH_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11326.03683344597</v>
+        <v>20345.13460673676</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>106.423854625953</v>
+        <v>142.636371962893</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.72747893371067</v>
+        <v>110.8456610852945</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9728303145931853</v>
+        <v>0.9507572465312571</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.898824052369938</v>
+        <v>4.180214185658127</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2669.243450980392</v>
+        <v>2666.044341085272</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2670.119726360875</v>
+        <v>2577.22697350197</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2649.818602195333</v>
+        <v>2642.200808003331</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2655.070743197006</v>
+        <v>2557.57784426258</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/ETH_USDT/metrics/ETH_USDT_metrics.xlsx
+++ b/artifacts/ETH_USDT/metrics/ETH_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20345.13460673676</v>
+        <v>12489.08239710687</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>142.636371962893</v>
+        <v>111.7545632048503</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>110.8456610852945</v>
+        <v>81.39466306213735</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9507572465312571</v>
+        <v>0.9697908544534809</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.180214185658127</v>
+        <v>3.057106434244671</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2666.044341085272</v>
+        <v>2665.209341085271</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2577.22697350197</v>
+        <v>2634.189242252388</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2642.200808003331</v>
+        <v>2641.049456948372</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2557.57784426258</v>
+        <v>2613.506889863764</v>
       </c>
     </row>
   </sheetData>
